--- a/output/2026-10-06_20_Serbia_Grad_Beograd_Cleaning.xlsx
+++ b/output/2026-10-06_20_Serbia_Grad_Beograd_Cleaning.xlsx
@@ -494,7 +494,6 @@
           <t>060/3047-197</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Distributore all'ingrosso confermato via sito ufficiale (correcto.rs): vende macchine lavapavimenti, aspiratori industriali, idropulitrici, pulitrici a vapore, estrattori per pulizia profonda, prodotti chimici, ricambi; offre anche noleggio/manutenzione. Fonti: planplus.rs, correcto.rs</t>
@@ -502,7 +501,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -512,7 +511,6 @@
           <t>Bent Excellent</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Beograd (Zemun, Altina)</t>
@@ -528,7 +526,6 @@
           <t>011/316-7751</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Rivenditore/distributore di attrezzature per la pulizia industriale, categoria 'Professional Tool Stores'; descritto come dealer/filiale di gruppo con casa madre in Slovenia, attivo dal 1971/1990. Nessun sito web verificabile trovato. Fonte: planplus.rs</t>
@@ -536,7 +533,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
